--- a/EL MIRADOR/PROTOTIPO-ELMIRADOR.xlsx
+++ b/EL MIRADOR/PROTOTIPO-ELMIRADOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E64B61-DC1C-46D5-A59F-CDA783193FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192B7254-FEEB-4468-9240-B25440519FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="293">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -47,15 +47,6 @@
   </si>
   <si>
     <t>ABONOS Y SERVICIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seguro Poliza </t>
-  </si>
-  <si>
-    <t>EDESUR</t>
-  </si>
-  <si>
-    <t>AYSA</t>
   </si>
   <si>
     <t>TOTAL ABONOS Y SERVICIOS</t>
@@ -765,30 +756,6 @@
     <t>UF 93,20%</t>
   </si>
   <si>
-    <t>Seguro obligatorio Sres encargados</t>
-  </si>
-  <si>
-    <t>ADS - Mantenimiento de ascensores</t>
-  </si>
-  <si>
-    <t>Aportes y contribuciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fumigacion </t>
-  </si>
-  <si>
-    <t>Mantenimiento grupo electrogeno</t>
-  </si>
-  <si>
-    <t>Sr Piletero - Mantenimiento de Pileta</t>
-  </si>
-  <si>
-    <t>Insumos pileta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compra de Gasoil </t>
-  </si>
-  <si>
     <t>LOCAL 1 (1,08%)</t>
   </si>
   <si>
@@ -804,9 +771,6 @@
     <t>LOCAL 5 (1,74%)</t>
   </si>
   <si>
-    <t>Metrogas</t>
-  </si>
-  <si>
     <t>Fernandez, Cristian</t>
   </si>
   <si>
@@ -973,6 +937,9 @@
   </si>
   <si>
     <t>Lobalo Lorena - Vega Maximiliano</t>
+  </si>
+  <si>
+    <t>Papelera</t>
   </si>
 </sst>
 </file>
@@ -1776,7 +1743,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2070,6 +2037,9 @@
     <xf numFmtId="166" fontId="14" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2139,6 +2109,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2169,27 +2151,15 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="11" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2575,7 +2545,7 @@
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="95" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -2601,7 +2571,7 @@
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="65"/>
       <c r="B3" s="66" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" s="66"/>
       <c r="D3" s="66"/>
@@ -2614,7 +2584,7 @@
     <row r="4" spans="1:9" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65"/>
       <c r="B4" s="66" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C4" s="66"/>
       <c r="D4" s="66"/>
@@ -2629,10 +2599,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="69" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D5" s="69"/>
       <c r="E5" s="70"/>
@@ -2643,7 +2613,7 @@
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
@@ -2656,7 +2626,7 @@
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="68" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B7" s="69"/>
       <c r="C7" s="69"/>
@@ -2672,27 +2642,27 @@
     <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="209" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="210"/>
-      <c r="D14" s="211"/>
+      <c r="B14" s="212" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="213"/>
+      <c r="D14" s="214"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="212"/>
-      <c r="C15" s="213"/>
-      <c r="D15" s="214"/>
+      <c r="B15" s="215"/>
+      <c r="C15" s="216"/>
+      <c r="D15" s="217"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="212"/>
-      <c r="C16" s="213"/>
-      <c r="D16" s="214"/>
+      <c r="B16" s="215"/>
+      <c r="C16" s="216"/>
+      <c r="D16" s="217"/>
       <c r="H16" s="191"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="215"/>
-      <c r="C17" s="216"/>
-      <c r="D17" s="217"/>
+      <c r="B17" s="218"/>
+      <c r="C17" s="219"/>
+      <c r="D17" s="220"/>
       <c r="H17" s="191"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -2707,33 +2677,33 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="59" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B21" s="60"/>
       <c r="C21" s="61"/>
       <c r="D21" s="57"/>
       <c r="E21" s="193" t="s">
+        <v>230</v>
+      </c>
+      <c r="F21" s="193" t="s">
+        <v>231</v>
+      </c>
+      <c r="G21" s="193" t="s">
+        <v>232</v>
+      </c>
+      <c r="H21" s="193" t="s">
         <v>233</v>
       </c>
-      <c r="F21" s="193" t="s">
-        <v>242</v>
-      </c>
-      <c r="G21" s="193" t="s">
-        <v>243</v>
-      </c>
-      <c r="H21" s="193" t="s">
-        <v>244</v>
-      </c>
       <c r="I21" s="193" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="J21" s="194" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="116" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -2747,11 +2717,11 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="116" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="168">
+      <c r="D23" s="250">
         <v>1000000</v>
       </c>
       <c r="E23" s="129"/>
@@ -2767,7 +2737,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="168">
+      <c r="D24" s="250">
         <v>-10000</v>
       </c>
       <c r="E24" s="129"/>
@@ -2779,11 +2749,11 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="116" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="168">
+      <c r="D25" s="250">
         <v>0</v>
       </c>
       <c r="E25" s="129"/>
@@ -2795,7 +2765,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="189" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B26" s="186"/>
       <c r="C26" s="186"/>
@@ -2812,7 +2782,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="116" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -2826,11 +2796,11 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="116" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="168">
+      <c r="D28" s="250">
         <v>1000000</v>
       </c>
       <c r="E28" s="129"/>
@@ -2846,7 +2816,7 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="168">
+      <c r="D29" s="250">
         <v>-100000</v>
       </c>
       <c r="E29" s="129"/>
@@ -2858,11 +2828,11 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="116" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="168"/>
+      <c r="D30" s="250"/>
       <c r="E30" s="129"/>
       <c r="F30" s="129"/>
       <c r="G30" s="129"/>
@@ -2872,7 +2842,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="189" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B31" s="186"/>
       <c r="C31" s="186"/>
@@ -2932,7 +2902,7 @@
     </row>
     <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="92" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -3002,7 +2972,7 @@
     </row>
     <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="93" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B37" s="93"/>
       <c r="C37" s="93"/>
@@ -3033,7 +3003,7 @@
     </row>
     <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="92" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -3054,7 +3024,7 @@
     </row>
     <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -3096,7 +3066,7 @@
     </row>
     <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="93" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B41" s="93"/>
       <c r="C41" s="93"/>
@@ -3159,7 +3129,7 @@
     </row>
     <row r="45" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="93" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B45" s="93"/>
       <c r="C45" s="93"/>
@@ -3179,9 +3149,7 @@
       <c r="L45" s="142"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>239</v>
-      </c>
+      <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="109"/>
@@ -3194,9 +3162,7 @@
       <c r="L46" s="142"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>240</v>
-      </c>
+      <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="109"/>
@@ -3210,7 +3176,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="93" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B48" s="93"/>
       <c r="C48" s="93"/>
@@ -3252,73 +3218,76 @@
       <c r="L49" s="142"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="92" t="s">
-        <v>234</v>
-      </c>
+      <c r="A50" s="92"/>
       <c r="B50" s="6"/>
       <c r="C50" s="96"/>
-      <c r="D50" s="109">
-        <v>15000</v>
+      <c r="D50" s="249">
+        <v>7907</v>
       </c>
       <c r="E50" s="129">
         <f>D50*93.2%</f>
-        <v>13980</v>
+        <v>7369.3240000000005</v>
       </c>
       <c r="F50" s="129">
         <f>$D50*1.08%</f>
-        <v>162</v>
+        <v>85.395600000000002</v>
       </c>
       <c r="G50" s="129">
         <f>$D50*1.28%</f>
-        <v>192</v>
+        <v>101.20960000000001</v>
       </c>
       <c r="H50" s="129">
         <f>$D50*1.21%</f>
-        <v>181.5</v>
+        <v>95.674700000000001</v>
       </c>
       <c r="I50" s="129">
         <f>$D50*1.49%</f>
-        <v>223.5</v>
+        <v>117.8143</v>
       </c>
       <c r="J50" s="129">
         <f>D50*1.74%</f>
-        <v>261</v>
+        <v>137.58179999999999</v>
+      </c>
+      <c r="K50" s="105">
+        <f>SUM(E50:J50)</f>
+        <v>7907</v>
       </c>
       <c r="L50" s="142"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="92" t="s">
-        <v>236</v>
-      </c>
+      <c r="A51" s="92"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
-      <c r="D51" s="109">
-        <f>102143.27+6011.02+54099.18</f>
-        <v>162253.47</v>
+      <c r="D51" s="249">
+        <v>160913</v>
       </c>
       <c r="E51" s="129">
         <f t="shared" ref="E51:E52" si="4">D51*93.2%</f>
-        <v>151220.23404000001</v>
+        <v>149970.916</v>
       </c>
       <c r="F51" s="129">
         <f>$D51*1.08%</f>
-        <v>1752.3374760000002</v>
+        <v>1737.8604</v>
       </c>
       <c r="G51" s="129">
         <f>$D51*1.28%</f>
-        <v>2076.8444159999999</v>
+        <v>2059.6864</v>
       </c>
       <c r="H51" s="129">
         <f>$D51*1.21%</f>
-        <v>1963.266987</v>
+        <v>1947.0473</v>
       </c>
       <c r="I51" s="129">
         <f>$D51*1.49%</f>
-        <v>2417.5767030000002</v>
+        <v>2397.6037000000001</v>
       </c>
       <c r="J51" s="129">
         <f>D51*1.74%</f>
-        <v>2823.2103779999998</v>
+        <v>2799.8861999999999</v>
+      </c>
+      <c r="K51" s="105">
+        <f t="shared" ref="K51:K52" si="5">SUM(E51:J51)</f>
+        <v>160913.00000000003</v>
       </c>
       <c r="L51" s="142"/>
     </row>
@@ -3326,18 +3295,36 @@
       <c r="A52" s="92"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
-      <c r="D52" s="109"/>
+      <c r="D52" s="109">
+        <v>7907</v>
+      </c>
       <c r="E52" s="129">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="129"/>
-      <c r="G52" s="129"/>
-      <c r="H52" s="129"/>
-      <c r="I52" s="129"/>
+        <v>7369.3240000000005</v>
+      </c>
+      <c r="F52" s="129">
+        <f>$D52*1.08%</f>
+        <v>85.395600000000002</v>
+      </c>
+      <c r="G52" s="129">
+        <f>$D52*1.28%</f>
+        <v>101.20960000000001</v>
+      </c>
+      <c r="H52" s="129">
+        <f>$D52*1.21%</f>
+        <v>95.674700000000001</v>
+      </c>
+      <c r="I52" s="129">
+        <f>$D52*1.49%</f>
+        <v>117.8143</v>
+      </c>
       <c r="J52" s="129">
-        <f t="shared" ref="J52" si="5">D52*6.8%</f>
-        <v>0</v>
+        <f>D52*1.74%</f>
+        <v>137.58179999999999</v>
+      </c>
+      <c r="K52" s="105">
+        <f t="shared" si="5"/>
+        <v>7907</v>
       </c>
       <c r="L52" s="142"/>
     </row>
@@ -3349,35 +3336,35 @@
       <c r="C53" s="94"/>
       <c r="D53" s="104">
         <f>SUM(D50:D52)</f>
-        <v>177253.47</v>
+        <v>176727</v>
       </c>
       <c r="E53" s="104">
         <f>SUM(E50:E52)</f>
-        <v>165200.23404000001</v>
+        <v>164709.56399999998</v>
       </c>
       <c r="F53" s="104">
         <f t="shared" ref="F53:I53" si="6">SUM(F50:F52)</f>
-        <v>1914.3374760000002</v>
+        <v>1908.6516000000001</v>
       </c>
       <c r="G53" s="104">
         <f t="shared" si="6"/>
-        <v>2268.8444159999999</v>
+        <v>2262.1056000000003</v>
       </c>
       <c r="H53" s="104">
         <f t="shared" si="6"/>
-        <v>2144.766987</v>
+        <v>2138.3966999999998</v>
       </c>
       <c r="I53" s="104">
         <f t="shared" si="6"/>
-        <v>2641.0767030000002</v>
+        <v>2633.2323000000001</v>
       </c>
       <c r="J53" s="104">
         <f>SUM(J50:J52)</f>
-        <v>3084.2103779999998</v>
+        <v>3075.0497999999998</v>
       </c>
       <c r="K53" s="105">
         <f>E53+J53+F53+G53+H53+I53</f>
-        <v>177253.47</v>
+        <v>176727.00000000003</v>
       </c>
       <c r="L53" s="142" t="str">
         <f>IF(D53=K53, "", "Error")</f>
@@ -3400,17 +3387,13 @@
       <c r="L54" s="142"/>
     </row>
     <row r="55" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="174" t="s">
-        <v>235</v>
-      </c>
+      <c r="A55" s="174"/>
       <c r="B55" s="163"/>
       <c r="C55" s="164"/>
-      <c r="D55" s="109">
-        <v>200000</v>
-      </c>
+      <c r="D55" s="109"/>
       <c r="E55" s="141">
         <f>D55</f>
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="F55" s="141"/>
       <c r="G55" s="141"/>
@@ -3419,11 +3402,11 @@
       <c r="J55" s="6"/>
       <c r="K55" s="105">
         <f t="shared" ref="K55:K62" si="7">D55</f>
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="L55" s="151">
         <f>E55+J55</f>
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M55" s="165">
         <f>L55-D55</f>
@@ -3435,45 +3418,41 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="92" t="s">
-        <v>7</v>
-      </c>
+      <c r="A56" s="92"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
-      <c r="D56" s="109">
-        <v>190000</v>
-      </c>
+      <c r="D56" s="109"/>
       <c r="E56" s="141">
         <f>D56*93.2%</f>
-        <v>177080</v>
+        <v>0</v>
       </c>
       <c r="F56" s="129">
         <f>$D56*1.08%</f>
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G56" s="129">
         <f>$D56*1.28%</f>
-        <v>2432</v>
+        <v>0</v>
       </c>
       <c r="H56" s="129">
         <f>$D56*1.21%</f>
-        <v>2299</v>
+        <v>0</v>
       </c>
       <c r="I56" s="129">
         <f>$D56*1.49%</f>
-        <v>2831</v>
+        <v>0</v>
       </c>
       <c r="J56" s="129">
         <f>D56*1.74%</f>
-        <v>3305.9999999999995</v>
+        <v>0</v>
       </c>
       <c r="K56" s="105">
         <f t="shared" si="7"/>
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="L56" s="151">
         <f>E56+J56+I56+H56+G56+F56</f>
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="M56" s="165">
         <f>L56-D56</f>
@@ -3485,45 +3464,41 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="92" t="s">
-        <v>9</v>
-      </c>
+      <c r="A57" s="92"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
-      <c r="D57" s="109">
-        <v>800000</v>
-      </c>
+      <c r="D57" s="109"/>
       <c r="E57" s="141">
         <f>D57*93.2%</f>
-        <v>745600</v>
+        <v>0</v>
       </c>
       <c r="F57" s="129">
         <f>$D57*1.08%</f>
-        <v>8640</v>
+        <v>0</v>
       </c>
       <c r="G57" s="129">
         <f>$D57*1.28%</f>
-        <v>10240</v>
+        <v>0</v>
       </c>
       <c r="H57" s="129">
         <f>$D57*1.21%</f>
-        <v>9680</v>
+        <v>0</v>
       </c>
       <c r="I57" s="129">
         <f>$D57*1.49%</f>
-        <v>11920</v>
+        <v>0</v>
       </c>
       <c r="J57" s="129">
         <f>D57*1.74%</f>
-        <v>13919.999999999998</v>
+        <v>0</v>
       </c>
       <c r="K57" s="105">
         <f t="shared" si="7"/>
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="L57" s="151">
         <f>E57+J57+I57+H57+G57+F57</f>
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="M57" s="165">
         <f>L57-D57</f>
@@ -3535,17 +3510,13 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>247</v>
-      </c>
+      <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
-      <c r="D58" s="109">
-        <v>800000</v>
-      </c>
+      <c r="D58" s="109"/>
       <c r="E58" s="141">
         <f>D58</f>
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="F58" s="129"/>
       <c r="G58" s="129"/>
@@ -3554,55 +3525,51 @@
       <c r="J58" s="129"/>
       <c r="K58" s="105">
         <f t="shared" si="7"/>
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="L58" s="151">
         <f>E58+J58+I58+H58+G58+F58</f>
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="M58" s="165"/>
       <c r="N58" s="165"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="124" t="s">
-        <v>8</v>
-      </c>
+      <c r="A59" s="124"/>
       <c r="B59" s="96"/>
       <c r="C59" s="96"/>
-      <c r="D59" s="109">
-        <v>846331.1</v>
-      </c>
+      <c r="D59" s="109"/>
       <c r="E59" s="141">
         <f>D59*93.2%</f>
-        <v>788780.58519999997</v>
+        <v>0</v>
       </c>
       <c r="F59" s="129">
         <f>$D59*1.08%</f>
-        <v>9140.3758799999996</v>
+        <v>0</v>
       </c>
       <c r="G59" s="129">
         <f>$D59*1.28%</f>
-        <v>10833.03808</v>
+        <v>0</v>
       </c>
       <c r="H59" s="129">
         <f>$D59*1.21%</f>
-        <v>10240.606309999999</v>
+        <v>0</v>
       </c>
       <c r="I59" s="129">
         <f>$D59*1.49%</f>
-        <v>12610.33339</v>
+        <v>0</v>
       </c>
       <c r="J59" s="129">
         <f>D59*1.74%</f>
-        <v>14726.161139999998</v>
+        <v>0</v>
       </c>
       <c r="K59" s="105">
         <f t="shared" si="7"/>
-        <v>846331.1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="151">
         <f t="shared" ref="L59:L62" si="8">E59+J59+I59+H59+G59+F59</f>
-        <v>846331.09999999986</v>
+        <v>0</v>
       </c>
       <c r="M59" s="165">
         <f>L59-D59</f>
@@ -3614,17 +3581,13 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="190" t="s">
-        <v>238</v>
-      </c>
+      <c r="A60" s="190"/>
       <c r="B60" s="166"/>
       <c r="C60" s="167"/>
-      <c r="D60" s="109">
-        <v>100000</v>
-      </c>
+      <c r="D60" s="109"/>
       <c r="E60" s="141">
         <f>D60</f>
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="F60" s="141"/>
       <c r="G60" s="141"/>
@@ -3633,11 +3596,11 @@
       <c r="J60" s="129"/>
       <c r="K60" s="105">
         <f t="shared" si="7"/>
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="L60" s="151">
         <f t="shared" si="8"/>
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="M60" s="165"/>
       <c r="N60" s="165">
@@ -3646,17 +3609,13 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="223" t="s">
-        <v>237</v>
-      </c>
-      <c r="B61" s="224"/>
-      <c r="C61" s="225"/>
-      <c r="D61" s="109">
-        <v>80000</v>
-      </c>
+      <c r="A61" s="226"/>
+      <c r="B61" s="227"/>
+      <c r="C61" s="228"/>
+      <c r="D61" s="109"/>
       <c r="E61" s="141">
         <f t="shared" ref="E61:E62" si="9">D61</f>
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F61" s="141"/>
       <c r="G61" s="141"/>
@@ -3665,11 +3624,11 @@
       <c r="J61" s="129"/>
       <c r="K61" s="105">
         <f t="shared" si="7"/>
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="L61" s="151">
         <f t="shared" si="8"/>
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="M61" s="165">
         <f>L61-D61</f>
@@ -3681,17 +3640,13 @@
       </c>
     </row>
     <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="177" t="s">
-        <v>241</v>
-      </c>
+      <c r="A62" s="177"/>
       <c r="B62" s="178"/>
       <c r="C62" s="173"/>
-      <c r="D62" s="109">
-        <v>150000</v>
-      </c>
+      <c r="D62" s="109"/>
       <c r="E62" s="141">
         <f t="shared" si="9"/>
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="F62" s="141"/>
       <c r="G62" s="141"/>
@@ -3700,11 +3655,11 @@
       <c r="J62" s="129"/>
       <c r="K62" s="105">
         <f t="shared" si="7"/>
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L62" s="151">
         <f t="shared" si="8"/>
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M62" s="165">
         <f>L62-D62</f>
@@ -3735,41 +3690,41 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="94" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B64" s="94"/>
       <c r="C64" s="94"/>
       <c r="D64" s="104">
         <f>SUM(D55:D63)</f>
-        <v>3166331.1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="104">
         <f>SUM(E55:E63)</f>
-        <v>3041460.5852000001</v>
+        <v>0</v>
       </c>
       <c r="F64" s="104">
         <f t="shared" ref="F64:I64" si="10">SUM(F55:F63)</f>
-        <v>19832.37588</v>
+        <v>0</v>
       </c>
       <c r="G64" s="104">
         <f t="shared" si="10"/>
-        <v>23505.038079999998</v>
+        <v>0</v>
       </c>
       <c r="H64" s="104">
         <f t="shared" si="10"/>
-        <v>22219.606309999999</v>
+        <v>0</v>
       </c>
       <c r="I64" s="104">
         <f t="shared" si="10"/>
-        <v>27361.33339</v>
+        <v>0</v>
       </c>
       <c r="J64" s="104">
         <f>SUM(J55:J63)</f>
-        <v>31952.161139999997</v>
+        <v>0</v>
       </c>
       <c r="K64" s="105">
         <f>E64+J64+F64+G64+H64+I64</f>
-        <v>3166331.1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="142" t="str">
         <f>IF(D64=K64, "", "Error")</f>
@@ -3821,48 +3776,51 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="92" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B68" s="96"/>
       <c r="C68" s="6"/>
-      <c r="D68" s="109">
-        <v>330000</v>
-      </c>
+      <c r="D68" s="109"/>
       <c r="E68" s="141">
         <f>D68*93.2%</f>
-        <v>307560</v>
+        <v>0</v>
       </c>
       <c r="F68" s="129">
         <f>$D68*1.08%</f>
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="G68" s="129">
         <f>$D68*1.28%</f>
-        <v>4224</v>
+        <v>0</v>
       </c>
       <c r="H68" s="129">
         <f>$D68*1.21%</f>
-        <v>3993</v>
+        <v>0</v>
       </c>
       <c r="I68" s="129">
         <f>$D68*1.49%</f>
-        <v>4917</v>
+        <v>0</v>
       </c>
       <c r="J68" s="129">
         <f>D68*1.74%</f>
-        <v>5742</v>
+        <v>0</v>
       </c>
       <c r="K68" s="150"/>
       <c r="L68" s="142"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="6"/>
+      <c r="A69" s="6" t="s">
+        <v>292</v>
+      </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
-      <c r="D69" s="109"/>
+      <c r="D69" s="249">
+        <f>9500+1900</f>
+        <v>11400</v>
+      </c>
       <c r="E69" s="152">
         <f>D69</f>
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="F69" s="152"/>
       <c r="G69" s="152"/>
@@ -3874,41 +3832,41 @@
     </row>
     <row r="70" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="93" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B70" s="93"/>
       <c r="C70" s="93"/>
       <c r="D70" s="103">
         <f>SUM(D68:D69)</f>
-        <v>330000</v>
+        <v>11400</v>
       </c>
       <c r="E70" s="103">
         <f>SUM(E68:E69)</f>
-        <v>307560</v>
+        <v>11400</v>
       </c>
       <c r="F70" s="103">
         <f t="shared" ref="F70:I70" si="11">SUM(F68:F69)</f>
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="G70" s="103">
         <f t="shared" si="11"/>
-        <v>4224</v>
+        <v>0</v>
       </c>
       <c r="H70" s="103">
         <f t="shared" si="11"/>
-        <v>3993</v>
+        <v>0</v>
       </c>
       <c r="I70" s="103">
         <f t="shared" si="11"/>
-        <v>4917</v>
+        <v>0</v>
       </c>
       <c r="J70" s="103">
         <f>SUM(J68:J69)</f>
-        <v>5742</v>
+        <v>0</v>
       </c>
       <c r="K70" s="105">
         <f>E70+J70+F70+G70+H70+I70</f>
-        <v>330000</v>
+        <v>11400</v>
       </c>
       <c r="L70" s="142" t="str">
         <f>IF(D70=K70, "", "Error")</f>
@@ -3944,7 +3902,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="92" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -3959,13 +3917,13 @@
     </row>
     <row r="74" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="92" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C74" s="6"/>
-      <c r="D74" s="109">
+      <c r="D74" s="251">
         <v>700000</v>
       </c>
       <c r="E74" s="141">
@@ -4024,7 +3982,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="93" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B77" s="93"/>
       <c r="C77" s="93"/>
@@ -4068,111 +4026,107 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="92" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
-      <c r="D78" s="109">
-        <v>100104.56</v>
-      </c>
+      <c r="D78" s="109"/>
       <c r="E78" s="141">
         <f>D78*93.2%</f>
-        <v>93297.449919999999</v>
+        <v>0</v>
       </c>
       <c r="F78" s="129">
         <f>$D78*1.08%</f>
-        <v>1081.129248</v>
+        <v>0</v>
       </c>
       <c r="G78" s="129">
         <f>$D78*1.28%</f>
-        <v>1281.3383679999999</v>
+        <v>0</v>
       </c>
       <c r="H78" s="129">
         <f>$D78*1.21%</f>
-        <v>1211.2651759999999</v>
+        <v>0</v>
       </c>
       <c r="I78" s="129">
         <f>$D78*1.49%</f>
-        <v>1491.5579439999999</v>
+        <v>0</v>
       </c>
       <c r="J78" s="129">
         <f>D78*1.74%</f>
-        <v>1741.8193439999998</v>
+        <v>0</v>
       </c>
       <c r="L78" s="142"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="92" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="117"/>
-      <c r="D79" s="109">
-        <v>44400</v>
-      </c>
+      <c r="D79" s="109"/>
       <c r="E79" s="141">
         <f>D79*93.2%</f>
-        <v>41380.800000000003</v>
+        <v>0</v>
       </c>
       <c r="F79" s="129">
         <f>$D79*1.08%</f>
-        <v>479.52000000000004</v>
+        <v>0</v>
       </c>
       <c r="G79" s="129">
         <f>$D79*1.28%</f>
-        <v>568.32000000000005</v>
+        <v>0</v>
       </c>
       <c r="H79" s="129">
         <f>$D79*1.21%</f>
-        <v>537.24</v>
+        <v>0</v>
       </c>
       <c r="I79" s="129">
         <f>$D79*1.49%</f>
-        <v>661.56</v>
+        <v>0</v>
       </c>
       <c r="J79" s="129">
         <f>D79*1.74%</f>
-        <v>772.56</v>
+        <v>0</v>
       </c>
       <c r="L79" s="142"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="93" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B80" s="93"/>
       <c r="C80" s="93"/>
       <c r="D80" s="149">
         <f>SUM(D78:D79)</f>
-        <v>144504.56</v>
+        <v>0</v>
       </c>
       <c r="E80" s="139">
         <f t="shared" ref="E80:J80" si="13">SUM(E78:E79)</f>
-        <v>134678.24992</v>
+        <v>0</v>
       </c>
       <c r="F80" s="139">
         <f t="shared" si="13"/>
-        <v>1560.6492479999999</v>
+        <v>0</v>
       </c>
       <c r="G80" s="139">
         <f t="shared" si="13"/>
-        <v>1849.6583679999999</v>
+        <v>0</v>
       </c>
       <c r="H80" s="139">
         <f t="shared" si="13"/>
-        <v>1748.5051759999999</v>
+        <v>0</v>
       </c>
       <c r="I80" s="139">
         <f t="shared" si="13"/>
-        <v>2153.1179439999996</v>
+        <v>0</v>
       </c>
       <c r="J80" s="139">
         <f t="shared" si="13"/>
-        <v>2514.3793439999999</v>
+        <v>0</v>
       </c>
       <c r="K80" s="105">
         <f>E80+J80+F80+G80+H80+I80</f>
-        <v>144504.56</v>
+        <v>0</v>
       </c>
       <c r="L80" s="142" t="str">
         <f>IF(D80=K80, "", "Error")</f>
@@ -4194,7 +4148,7 @@
     </row>
     <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="197" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B82" s="198"/>
       <c r="C82" s="198"/>
@@ -4236,41 +4190,41 @@
     </row>
     <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B84" s="58"/>
       <c r="C84" s="4"/>
       <c r="D84" s="172">
         <f>SUM(D82+D80+D77+D70+D64+D53+D37+D32+D48)</f>
-        <v>6408089.1299999999</v>
+        <v>2778127</v>
       </c>
       <c r="E84" s="140">
         <f>SUM(E82+E80+E77+E70+E64+E53+E37+E32+E48)</f>
-        <v>6062779.0691599995</v>
+        <v>2589989.5640000002</v>
       </c>
       <c r="F84" s="140">
         <f t="shared" ref="F84:I84" si="14">SUM(F82+F80+F77+F70+F64+F53+F37+F32+F48)</f>
-        <v>54843.362604000002</v>
+        <v>29880.651600000001</v>
       </c>
       <c r="G84" s="140">
         <f t="shared" si="14"/>
-        <v>64999.540864000002</v>
+        <v>35414.105600000003</v>
       </c>
       <c r="H84" s="140">
         <f t="shared" si="14"/>
-        <v>61444.878473000004</v>
+        <v>33477.396699999998</v>
       </c>
       <c r="I84" s="140">
         <f t="shared" si="14"/>
-        <v>75663.528036999996</v>
+        <v>41224.232300000003</v>
       </c>
       <c r="J84" s="140">
         <f>SUM(J82+J80+J77+J70+J64+J53+J37+J32+J48)</f>
-        <v>88358.750862000001</v>
+        <v>48141.049800000001</v>
       </c>
       <c r="K84" s="105">
         <f>E84+J84+F84+G84+H84+I84</f>
-        <v>6408089.129999999</v>
+        <v>2778127</v>
       </c>
       <c r="L84" s="142" t="str">
         <f>IF(D84=K84, "", "Error")</f>
@@ -4291,7 +4245,7 @@
     </row>
     <row r="86" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="136" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B86" s="135"/>
       <c r="C86" s="135"/>
@@ -4321,7 +4275,7 @@
     </row>
     <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="137" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B89" s="138"/>
       <c r="C89" s="134">
@@ -4349,26 +4303,26 @@
       <c r="I91" s="131"/>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="221" t="s">
-        <v>87</v>
-      </c>
-      <c r="B92" s="222"/>
-      <c r="C92" s="222"/>
-      <c r="D92" s="222"/>
+      <c r="A92" s="224" t="s">
+        <v>84</v>
+      </c>
+      <c r="B92" s="225"/>
+      <c r="C92" s="225"/>
+      <c r="D92" s="225"/>
       <c r="E92" s="158" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F92" s="158"/>
       <c r="G92" s="158"/>
       <c r="H92" s="158"/>
       <c r="I92" s="158"/>
       <c r="J92" s="159" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="226"/>
-      <c r="B93" s="227"/>
+      <c r="A93" s="229"/>
+      <c r="B93" s="230"/>
       <c r="C93" s="160"/>
       <c r="D93" s="109"/>
       <c r="E93" s="141">
@@ -4382,8 +4336,8 @@
       <c r="J93" s="129"/>
     </row>
     <row r="94" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="226"/>
-      <c r="B94" s="227"/>
+      <c r="A94" s="229"/>
+      <c r="B94" s="230"/>
       <c r="C94" s="160"/>
       <c r="D94" s="109"/>
       <c r="E94" s="141"/>
@@ -4394,11 +4348,11 @@
       <c r="J94" s="129"/>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="218" t="s">
-        <v>27</v>
-      </c>
-      <c r="B95" s="219"/>
-      <c r="C95" s="220"/>
+      <c r="A95" s="221" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95" s="222"/>
+      <c r="C95" s="223"/>
       <c r="D95" s="157">
         <f>SUM(D93:D94)</f>
         <v>0</v>
@@ -4433,25 +4387,25 @@
     </row>
     <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="99" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B98" s="100">
         <f>D84</f>
-        <v>6408089.1299999999</v>
+        <v>2778127</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="101" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B99" s="102">
         <f>D84-D82</f>
-        <v>6408089.1299999999</v>
+        <v>2778127</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D100" s="208"/>
-      <c r="E100" s="208"/>
+      <c r="D100" s="211"/>
+      <c r="E100" s="211"/>
       <c r="F100" s="179"/>
       <c r="G100" s="179"/>
       <c r="H100" s="179"/>
@@ -4459,12 +4413,12 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="72" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B101" s="73"/>
       <c r="C101" s="74"/>
-      <c r="D101" s="208"/>
-      <c r="E101" s="208"/>
+      <c r="D101" s="211"/>
+      <c r="E101" s="211"/>
       <c r="F101" s="179"/>
       <c r="G101" s="179"/>
       <c r="H101" s="179"/>
@@ -4472,14 +4426,14 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="75" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B102" s="9">
         <v>0</v>
       </c>
       <c r="C102" s="76"/>
-      <c r="D102" s="208"/>
-      <c r="E102" s="208"/>
+      <c r="D102" s="211"/>
+      <c r="E102" s="211"/>
       <c r="F102" s="179"/>
       <c r="G102" s="179"/>
       <c r="H102" s="179"/>
@@ -4487,17 +4441,17 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="77" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B103" s="90">
         <f>PRORRATEO!G126</f>
         <v>0</v>
       </c>
       <c r="C103" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="D103" s="208"/>
-      <c r="E103" s="208"/>
+        <v>67</v>
+      </c>
+      <c r="D103" s="211"/>
+      <c r="E103" s="211"/>
       <c r="F103" s="179"/>
       <c r="G103" s="179"/>
       <c r="H103" s="179"/>
@@ -4505,15 +4459,15 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="77" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B104" s="162">
         <f>-B99</f>
-        <v>-6408089.1299999999</v>
+        <v>-2778127</v>
       </c>
       <c r="C104" s="74"/>
-      <c r="D104" s="208"/>
-      <c r="E104" s="208"/>
+      <c r="D104" s="211"/>
+      <c r="E104" s="211"/>
       <c r="F104" s="179"/>
       <c r="G104" s="179"/>
       <c r="H104" s="179"/>
@@ -4522,15 +4476,15 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="77" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B105" s="162">
         <f>-D95</f>
         <v>0</v>
       </c>
       <c r="C105" s="74"/>
-      <c r="D105" s="208"/>
-      <c r="E105" s="208"/>
+      <c r="D105" s="211"/>
+      <c r="E105" s="211"/>
       <c r="F105" s="179"/>
       <c r="G105" s="179"/>
       <c r="H105" s="179"/>
@@ -4539,7 +4493,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="77" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B106" s="162">
         <f>-B113</f>
@@ -4549,7 +4503,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="77" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B107" s="91">
         <f>-C89</f>
@@ -4564,11 +4518,11 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="75" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B109" s="79">
         <f>SUM(B102:B108)</f>
-        <v>-6408089.1299999999</v>
+        <v>-2778127</v>
       </c>
       <c r="C109" s="146"/>
     </row>
@@ -4588,7 +4542,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="72" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B112" s="9">
         <v>0</v>
@@ -4604,7 +4558,7 @@
     </row>
     <row r="113" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="75" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B113" s="91"/>
       <c r="C113" s="80"/>
@@ -4627,7 +4581,7 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="97" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B115" s="98">
         <f>SUM(B112:B114)</f>
@@ -4647,50 +4601,50 @@
       <c r="R119" s="10"/>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B122" s="207"/>
-      <c r="C122" s="207"/>
-      <c r="D122" s="207"/>
-      <c r="E122" s="207"/>
+      <c r="B122" s="210"/>
+      <c r="C122" s="210"/>
+      <c r="D122" s="210"/>
+      <c r="E122" s="210"/>
       <c r="F122" s="185"/>
       <c r="G122" s="185"/>
       <c r="H122" s="185"/>
       <c r="I122" s="185"/>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B123" s="207"/>
-      <c r="C123" s="207"/>
-      <c r="D123" s="207"/>
-      <c r="E123" s="207"/>
+      <c r="B123" s="210"/>
+      <c r="C123" s="210"/>
+      <c r="D123" s="210"/>
+      <c r="E123" s="210"/>
       <c r="F123" s="185"/>
       <c r="G123" s="185"/>
       <c r="H123" s="185"/>
       <c r="I123" s="185"/>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B124" s="207"/>
-      <c r="C124" s="207"/>
-      <c r="D124" s="207"/>
-      <c r="E124" s="207"/>
+      <c r="B124" s="210"/>
+      <c r="C124" s="210"/>
+      <c r="D124" s="210"/>
+      <c r="E124" s="210"/>
       <c r="F124" s="185"/>
       <c r="G124" s="185"/>
       <c r="H124" s="185"/>
       <c r="I124" s="185"/>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B125" s="207"/>
-      <c r="C125" s="207"/>
-      <c r="D125" s="207"/>
-      <c r="E125" s="207"/>
+      <c r="B125" s="210"/>
+      <c r="C125" s="210"/>
+      <c r="D125" s="210"/>
+      <c r="E125" s="210"/>
       <c r="F125" s="185"/>
       <c r="G125" s="185"/>
       <c r="H125" s="185"/>
       <c r="I125" s="185"/>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B126" s="207"/>
-      <c r="C126" s="207"/>
-      <c r="D126" s="207"/>
-      <c r="E126" s="207"/>
+      <c r="B126" s="210"/>
+      <c r="C126" s="210"/>
+      <c r="D126" s="210"/>
+      <c r="E126" s="210"/>
       <c r="F126" s="185"/>
       <c r="G126" s="185"/>
       <c r="H126" s="185"/>
@@ -4741,19 +4695,19 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="K1" s="231">
+        <v>93</v>
+      </c>
+      <c r="K1" s="238">
         <f>RESUMEN!D84</f>
-        <v>6408089.1299999999</v>
-      </c>
-      <c r="L1" s="232"/>
+        <v>2778127</v>
+      </c>
+      <c r="L1" s="239"/>
       <c r="M1" s="144"/>
       <c r="N1" s="130"/>
     </row>
@@ -4768,7 +4722,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="144">
@@ -4816,75 +4770,75 @@
       <c r="M4" s="119"/>
       <c r="O4" s="165">
         <f>K1-J126</f>
-        <v>615378.24316001497</v>
+        <v>-3014583.8868399849</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="228" t="s">
+      <c r="A5" s="231" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="233" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="231" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="240" t="s">
+      <c r="E5" s="231" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="231" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="228" t="s">
+      <c r="G5" s="231" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="242" t="s">
+      <c r="H5" s="242" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="228" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="228" t="s">
+      <c r="I5" s="240" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="228" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="235" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="233" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="233" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="238" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="233" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="233" t="s">
-        <v>46</v>
+      <c r="J5" s="240" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="245" t="s">
+        <v>92</v>
+      </c>
+      <c r="L5" s="240" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="240" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="229"/>
-      <c r="B6" s="241"/>
-      <c r="C6" s="229"/>
-      <c r="D6" s="243"/>
-      <c r="E6" s="229"/>
-      <c r="F6" s="229"/>
-      <c r="G6" s="229"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="234"/>
-      <c r="J6" s="237"/>
-      <c r="K6" s="239"/>
-      <c r="L6" s="237"/>
-      <c r="M6" s="234"/>
+      <c r="A6" s="232"/>
+      <c r="B6" s="234"/>
+      <c r="C6" s="232"/>
+      <c r="D6" s="236"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="241"/>
+      <c r="J6" s="244"/>
+      <c r="K6" s="246"/>
+      <c r="L6" s="244"/>
+      <c r="M6" s="241"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D7" s="128" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="E7" s="184">
         <v>1.0800000000000001E-2</v>
@@ -4917,10 +4871,10 @@
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D8" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E8" s="184">
         <v>1.2800000000000001E-2</v>
@@ -4952,14 +4906,14 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D9" s="128" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="E9" s="184">
         <v>1.21E-2</v>
@@ -4991,14 +4945,14 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D10" s="128" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E10" s="184">
         <v>1.49E-2</v>
@@ -5030,14 +4984,14 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="128" t="s">
         <v>179</v>
-      </c>
-      <c r="D11" s="128" t="s">
-        <v>182</v>
       </c>
       <c r="E11" s="184">
         <v>1.7399999999999999E-2</v>
@@ -5069,14 +5023,14 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="246" t="s">
-        <v>251</v>
+        <v>104</v>
+      </c>
+      <c r="D12" s="207" t="s">
+        <v>239</v>
       </c>
       <c r="E12" s="183">
         <v>1.8800000000000001E-2</v>
@@ -5110,14 +5064,14 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="246" t="s">
-        <v>252</v>
+        <v>105</v>
+      </c>
+      <c r="D13" s="207" t="s">
+        <v>240</v>
       </c>
       <c r="E13" s="183">
         <v>8.3999999999999995E-3</v>
@@ -5151,14 +5105,14 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" s="246" t="s">
-        <v>253</v>
+        <v>106</v>
+      </c>
+      <c r="D14" s="207" t="s">
+        <v>241</v>
       </c>
       <c r="E14" s="183">
         <v>2.01E-2</v>
@@ -5192,14 +5146,14 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="246" t="s">
-        <v>254</v>
+        <v>107</v>
+      </c>
+      <c r="D15" s="207" t="s">
+        <v>242</v>
       </c>
       <c r="E15" s="183">
         <v>9.4000000000000004E-3</v>
@@ -5233,14 +5187,14 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D16" s="128" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E16" s="183">
         <v>8.6999999999999994E-3</v>
@@ -5273,14 +5227,14 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D17" s="128" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E17" s="183">
         <v>9.4999999999999998E-3</v>
@@ -5314,14 +5268,14 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D18" s="128" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E18" s="183">
         <v>1.6500000000000001E-2</v>
@@ -5355,14 +5309,14 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D19" s="128" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E19" s="183">
         <v>7.3000000000000001E-3</v>
@@ -5396,14 +5350,14 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E20" s="183">
         <v>1.78E-2</v>
@@ -5437,14 +5391,14 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D21" s="128" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E21" s="183">
         <v>9.4000000000000004E-3</v>
@@ -5478,14 +5432,14 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D22" s="128" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E22" s="183">
         <v>8.6999999999999994E-3</v>
@@ -5519,14 +5473,14 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D23" s="128" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E23" s="183">
         <v>9.4999999999999998E-3</v>
@@ -5559,14 +5513,14 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D24" s="128" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="E24" s="183">
         <v>1.6400000000000001E-2</v>
@@ -5600,14 +5554,14 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D25" s="128" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E25" s="183">
         <v>7.1999999999999998E-3</v>
@@ -5641,14 +5595,14 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D26" s="128" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="E26" s="183">
         <v>1.7299999999999999E-2</v>
@@ -5682,14 +5636,14 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D27" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E27" s="183">
         <v>9.4000000000000004E-3</v>
@@ -5723,14 +5677,14 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D28" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E28" s="183">
         <v>8.6999999999999994E-3</v>
@@ -5764,14 +5718,14 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D29" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E29" s="183">
         <v>9.4999999999999998E-3</v>
@@ -5805,14 +5759,14 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D30" s="128" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E30" s="183">
         <v>1.6400000000000001E-2</v>
@@ -5846,14 +5800,14 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D31" s="128" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="E31" s="183">
         <v>7.1999999999999998E-3</v>
@@ -5887,14 +5841,14 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D32" s="128" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E32" s="183">
         <v>1.7299999999999999E-2</v>
@@ -5928,14 +5882,14 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D33" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E33" s="183">
         <v>9.4000000000000004E-3</v>
@@ -5969,14 +5923,14 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D34" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E34" s="183">
         <v>8.6999999999999994E-3</v>
@@ -6010,14 +5964,14 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D35" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E35" s="183">
         <v>9.4999999999999998E-3</v>
@@ -6051,14 +6005,14 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D36" s="128" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E36" s="183">
         <v>1.6400000000000001E-2</v>
@@ -6092,14 +6046,14 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D37" s="128" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="E37" s="183">
         <v>7.1999999999999998E-3</v>
@@ -6133,14 +6087,14 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D38" s="128" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E38" s="183">
         <v>1.7299999999999999E-2</v>
@@ -6174,14 +6128,14 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D39" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E39" s="183">
         <v>9.4000000000000004E-3</v>
@@ -6215,14 +6169,14 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D40" s="128" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E40" s="183">
         <v>8.6999999999999994E-3</v>
@@ -6256,14 +6210,14 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D41" s="128" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E41" s="183">
         <v>9.4999999999999998E-3</v>
@@ -6297,14 +6251,14 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D42" s="128" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E42" s="183">
         <v>1.6400000000000001E-2</v>
@@ -6338,14 +6292,14 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D43" s="128" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="E43" s="183">
         <v>7.1999999999999998E-3</v>
@@ -6380,14 +6334,14 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D44" s="128" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E44" s="183">
         <v>1.7299999999999999E-2</v>
@@ -6422,14 +6376,14 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D45" s="128" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="E45" s="183">
         <v>9.4000000000000004E-3</v>
@@ -6463,14 +6417,14 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D46" s="128" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="E46" s="183">
         <v>8.6999999999999994E-3</v>
@@ -6504,14 +6458,14 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D47" s="128" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="E47" s="183">
         <v>9.4999999999999998E-3</v>
@@ -6545,14 +6499,14 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D48" s="128" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E48" s="183">
         <v>1.6400000000000001E-2</v>
@@ -6588,14 +6542,14 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D49" s="128" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="E49" s="183">
         <v>7.1999999999999998E-3</v>
@@ -6629,14 +6583,14 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D50" s="128" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="E50" s="183">
         <v>1.7299999999999999E-2</v>
@@ -6670,14 +6624,14 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D51" s="128" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E51" s="183">
         <v>9.4000000000000004E-3</v>
@@ -6711,14 +6665,14 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D52" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E52" s="183">
         <v>8.6999999999999994E-3</v>
@@ -6752,14 +6706,14 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D53" s="128" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E53" s="183">
         <v>9.4999999999999998E-3</v>
@@ -6793,14 +6747,14 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D54" s="128" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E54" s="183">
         <v>1.6400000000000001E-2</v>
@@ -6834,14 +6788,14 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D55" s="128" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E55" s="183">
         <v>7.1999999999999998E-3</v>
@@ -6875,14 +6829,14 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D56" s="128" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="E56" s="183">
         <v>1.7299999999999999E-2</v>
@@ -6916,14 +6870,14 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D57" s="128" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="E57" s="183">
         <v>9.4000000000000004E-3</v>
@@ -6957,14 +6911,14 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D58" s="128" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E58" s="183">
         <v>8.6999999999999994E-3</v>
@@ -6998,14 +6952,14 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D59" s="128" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E59" s="183">
         <v>9.4999999999999998E-3</v>
@@ -7039,14 +6993,14 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D60" s="128" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="E60" s="183">
         <v>1.6400000000000001E-2</v>
@@ -7080,14 +7034,14 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="128" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D61" s="128" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="E61" s="183">
         <v>7.1999999999999998E-3</v>
@@ -7121,14 +7075,14 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D62" s="128" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E62" s="183">
         <v>1.7299999999999999E-2</v>
@@ -7162,14 +7116,14 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D63" s="128" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E63" s="183">
         <v>9.4000000000000004E-3</v>
@@ -7203,14 +7157,14 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D64" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E64" s="183">
         <v>8.6999999999999994E-3</v>
@@ -7244,14 +7198,14 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D65" s="128" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E65" s="183">
         <v>9.4999999999999998E-3</v>
@@ -7285,14 +7239,14 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="128" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D66" s="128" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E66" s="183">
         <v>2.35E-2</v>
@@ -7326,14 +7280,14 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D67" s="128" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E67" s="183">
         <v>1.7299999999999999E-2</v>
@@ -7367,14 +7321,14 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D68" s="128" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="E68" s="183">
         <v>9.4000000000000004E-3</v>
@@ -7408,14 +7362,14 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D69" s="128" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E69" s="183">
         <v>8.6999999999999994E-3</v>
@@ -7449,14 +7403,14 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D70" s="128" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="E70" s="183">
         <v>9.4999999999999998E-3</v>
@@ -7490,14 +7444,14 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="128" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D71" s="128" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E71" s="183">
         <v>2.35E-2</v>
@@ -7531,14 +7485,14 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D72" s="128" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E72" s="183">
         <v>1.7299999999999999E-2</v>
@@ -7572,14 +7526,14 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D73" s="128" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="E73" s="183">
         <v>9.4000000000000004E-3</v>
@@ -7613,14 +7567,14 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D74" s="128" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="E74" s="183">
         <v>8.6999999999999994E-3</v>
@@ -7654,14 +7608,14 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D75" s="128" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E75" s="183">
         <v>9.4999999999999998E-3</v>
@@ -7695,14 +7649,14 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="128" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D76" s="128" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E76" s="183">
         <v>2.35E-2</v>
@@ -7736,14 +7690,14 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="128" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D77" s="128" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="E77" s="183">
         <v>1.7299999999999999E-2</v>
@@ -7777,14 +7731,14 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B78" s="6"/>
       <c r="C78" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D78" s="128" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="E78" s="183">
         <v>9.4000000000000004E-3</v>
@@ -7818,14 +7772,14 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D79" s="128" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="E79" s="183">
         <v>8.6999999999999994E-3</v>
@@ -7859,14 +7813,14 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="128" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B80" s="6"/>
       <c r="C80" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D80" s="128" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="E80" s="183">
         <v>9.4999999999999998E-3</v>
@@ -7902,10 +7856,10 @@
       <c r="A81" s="128"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D81" s="128" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="E81" s="184">
         <v>2.3E-3</v>
@@ -7941,10 +7895,10 @@
       <c r="A82" s="128"/>
       <c r="B82" s="6"/>
       <c r="C82" s="181" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D82" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E82" s="184">
         <v>2.3E-3</v>
@@ -7980,10 +7934,10 @@
       <c r="A83" s="128"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D83" s="128" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="E83" s="184">
         <v>2.3E-3</v>
@@ -8019,10 +7973,10 @@
       <c r="A84" s="128"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D84" s="128" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="E84" s="184">
         <v>2.3E-3</v>
@@ -8058,10 +8012,10 @@
       <c r="A85" s="128"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D85" s="128" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E85" s="184">
         <v>2.3E-3</v>
@@ -8097,10 +8051,10 @@
       <c r="A86" s="128"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D86" s="128" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="E86" s="184">
         <v>2.3E-3</v>
@@ -8136,10 +8090,10 @@
       <c r="A87" s="128"/>
       <c r="B87" s="6"/>
       <c r="C87" s="96" t="s">
-        <v>193</v>
-      </c>
-      <c r="D87" s="246" t="s">
-        <v>267</v>
+        <v>190</v>
+      </c>
+      <c r="D87" s="207" t="s">
+        <v>255</v>
       </c>
       <c r="E87" s="184">
         <v>2.3E-3</v>
@@ -8175,10 +8129,10 @@
       <c r="A88" s="128"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D88" s="128" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E88" s="184">
         <v>2.3E-3</v>
@@ -8214,10 +8168,10 @@
       <c r="A89" s="128"/>
       <c r="B89" s="6"/>
       <c r="C89" s="181" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D89" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E89" s="184">
         <v>2.3E-3</v>
@@ -8253,10 +8207,10 @@
       <c r="A90" s="128"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D90" s="128" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="E90" s="184">
         <v>2.3E-3</v>
@@ -8292,10 +8246,10 @@
       <c r="A91" s="128"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D91" s="128" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="E91" s="184">
         <v>2.3E-3</v>
@@ -8331,10 +8285,10 @@
       <c r="A92" s="128"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D92" s="128" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E92" s="184">
         <v>2.3E-3</v>
@@ -8370,10 +8324,10 @@
       <c r="A93" s="128"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D93" s="128" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="E93" s="184">
         <v>2.3E-3</v>
@@ -8409,10 +8363,10 @@
       <c r="A94" s="128"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D94" s="128" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="E94" s="184">
         <v>2.3E-3</v>
@@ -8448,10 +8402,10 @@
       <c r="A95" s="128"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D95" s="128" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E95" s="184">
         <v>2.3E-3</v>
@@ -8487,10 +8441,10 @@
       <c r="A96" s="128"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D96" s="128" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="E96" s="184">
         <v>2.3E-3</v>
@@ -8526,10 +8480,10 @@
       <c r="A97" s="128"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D97" s="128" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E97" s="184">
         <v>2.3E-3</v>
@@ -8564,11 +8518,11 @@
     <row r="98" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="128"/>
       <c r="B98" s="6"/>
-      <c r="C98" s="247" t="s">
-        <v>204</v>
-      </c>
-      <c r="D98" s="248" t="s">
-        <v>182</v>
+      <c r="C98" s="208" t="s">
+        <v>201</v>
+      </c>
+      <c r="D98" s="209" t="s">
+        <v>179</v>
       </c>
       <c r="E98" s="184">
         <v>2.3E-3</v>
@@ -8604,10 +8558,10 @@
       <c r="A99" s="128"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D99" s="128" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="E99" s="184">
         <v>2.3E-3</v>
@@ -8643,10 +8597,10 @@
       <c r="A100" s="128"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D100" s="128" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E100" s="184">
         <v>2.3E-3</v>
@@ -8682,10 +8636,10 @@
       <c r="A101" s="128"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D101" s="128" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E101" s="184">
         <v>2.3E-3</v>
@@ -8721,10 +8675,10 @@
       <c r="A102" s="128"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D102" s="128" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="E102" s="184">
         <v>2.3E-3</v>
@@ -8760,10 +8714,10 @@
       <c r="A103" s="128"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D103" s="128" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E103" s="184">
         <v>2.3E-3</v>
@@ -8787,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="L103" s="5">
-        <f t="shared" ref="L103:L134" si="16">J103+I103+H103+K103</f>
+        <f t="shared" ref="L103:L124" si="16">J103+I103+H103+K103</f>
         <v>13441.0183</v>
       </c>
       <c r="M103" s="9">
@@ -8799,10 +8753,10 @@
       <c r="A104" s="128"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D104" s="128" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E104" s="184">
         <v>2.3E-3</v>
@@ -8838,10 +8792,10 @@
       <c r="A105" s="128"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D105" s="128" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E105" s="184">
         <v>2.3E-3</v>
@@ -8877,10 +8831,10 @@
       <c r="A106" s="128"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D106" s="128" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E106" s="184">
         <v>2.3E-3</v>
@@ -8916,10 +8870,10 @@
       <c r="A107" s="128"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D107" s="128" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="E107" s="184">
         <v>2.3E-3</v>
@@ -8955,10 +8909,10 @@
       <c r="A108" s="128"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D108" s="128" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E108" s="184">
         <v>2.3E-3</v>
@@ -8994,10 +8948,10 @@
       <c r="A109" s="128"/>
       <c r="B109" s="6"/>
       <c r="C109" s="181" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D109" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E109" s="184">
         <v>2.3E-3</v>
@@ -9033,10 +8987,10 @@
       <c r="A110" s="128"/>
       <c r="B110" s="6"/>
       <c r="C110" s="181" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D110" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E110" s="184">
         <v>2.3E-3</v>
@@ -9072,10 +9026,10 @@
       <c r="A111" s="128"/>
       <c r="B111" s="6"/>
       <c r="C111" s="181" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D111" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E111" s="184">
         <v>2.3E-3</v>
@@ -9111,10 +9065,10 @@
       <c r="A112" s="121"/>
       <c r="B112" s="6"/>
       <c r="C112" s="181" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D112" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E112" s="184">
         <v>2.3E-3</v>
@@ -9150,10 +9104,10 @@
       <c r="A113" s="121"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D113" s="128" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E113" s="184">
         <v>2.3E-3</v>
@@ -9189,10 +9143,10 @@
       <c r="A114" s="121"/>
       <c r="B114" s="6"/>
       <c r="C114" s="181" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D114" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E114" s="184">
         <v>2.3E-3</v>
@@ -9228,10 +9182,10 @@
       <c r="A115" s="121"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D115" s="128" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="E115" s="184">
         <v>2.3E-3</v>
@@ -9267,10 +9221,10 @@
       <c r="A116" s="121"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D116" s="128" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E116" s="184">
         <v>2.3E-3</v>
@@ -9306,10 +9260,10 @@
       <c r="A117" s="121"/>
       <c r="B117" s="6"/>
       <c r="C117" s="181" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D117" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E117" s="184">
         <v>2.3E-3</v>
@@ -9345,10 +9299,10 @@
       <c r="A118" s="121"/>
       <c r="B118" s="6"/>
       <c r="C118" s="181" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D118" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E118" s="184">
         <v>2.3E-3</v>
@@ -9384,10 +9338,10 @@
       <c r="A119" s="121"/>
       <c r="B119" s="6"/>
       <c r="C119" s="181" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D119" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E119" s="184">
         <v>2.3E-3</v>
@@ -9423,10 +9377,10 @@
       <c r="A120" s="121"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D120" s="128" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="E120" s="184">
         <v>2.3E-3</v>
@@ -9462,10 +9416,10 @@
       <c r="A121" s="121"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D121" s="128" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E121" s="184">
         <v>2.3E-3</v>
@@ -9501,10 +9455,10 @@
       <c r="A122" s="121"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D122" s="128" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="E122" s="184">
         <v>2.3E-3</v>
@@ -9538,14 +9492,14 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="121" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B123" s="6"/>
       <c r="C123" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D123" s="128" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="E123" s="184">
         <v>2.3E-3</v>
@@ -9582,14 +9536,14 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="121" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B124" s="6"/>
       <c r="C124" s="181" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D124" s="182" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E124" s="184">
         <v>2.3E-3</v>
@@ -9626,7 +9580,7 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="121" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -9684,34 +9638,34 @@
     <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="J127" s="132">
         <f>J126-K1</f>
-        <v>-615378.24316001497</v>
+        <v>3014583.8868399849</v>
       </c>
     </row>
     <row r="128" spans="1:15" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C128" s="230"/>
-      <c r="D128" s="230"/>
-      <c r="E128" s="230"/>
-      <c r="F128" s="230"/>
-      <c r="G128" s="230"/>
-      <c r="H128" s="230"/>
-      <c r="I128" s="230"/>
-      <c r="J128" s="230"/>
-      <c r="K128" s="230"/>
-      <c r="L128" s="230"/>
-      <c r="M128" s="230"/>
+      <c r="C128" s="237"/>
+      <c r="D128" s="237"/>
+      <c r="E128" s="237"/>
+      <c r="F128" s="237"/>
+      <c r="G128" s="237"/>
+      <c r="H128" s="237"/>
+      <c r="I128" s="237"/>
+      <c r="J128" s="237"/>
+      <c r="K128" s="237"/>
+      <c r="L128" s="237"/>
+      <c r="M128" s="237"/>
     </row>
     <row r="129" spans="3:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C129" s="230"/>
-      <c r="D129" s="230"/>
-      <c r="E129" s="230"/>
-      <c r="F129" s="230"/>
-      <c r="G129" s="230"/>
-      <c r="H129" s="230"/>
-      <c r="I129" s="230"/>
-      <c r="J129" s="230"/>
-      <c r="K129" s="230"/>
-      <c r="L129" s="230"/>
-      <c r="M129" s="230"/>
+      <c r="C129" s="237"/>
+      <c r="D129" s="237"/>
+      <c r="E129" s="237"/>
+      <c r="F129" s="237"/>
+      <c r="G129" s="237"/>
+      <c r="H129" s="237"/>
+      <c r="I129" s="237"/>
+      <c r="J129" s="237"/>
+      <c r="K129" s="237"/>
+      <c r="L129" s="237"/>
+      <c r="M129" s="237"/>
     </row>
     <row r="130" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C130" s="155"/>
@@ -9730,105 +9684,100 @@
       <c r="M130" s="155"/>
     </row>
     <row r="131" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C131" s="230" t="s">
-        <v>231</v>
-      </c>
-      <c r="D131" s="230"/>
-      <c r="E131" s="230"/>
-      <c r="F131" s="230"/>
-      <c r="G131" s="230"/>
-      <c r="H131" s="230"/>
-      <c r="I131" s="230"/>
-      <c r="J131" s="230"/>
-      <c r="K131" s="230"/>
-      <c r="L131" s="230"/>
-      <c r="M131" s="230"/>
+      <c r="C131" s="237" t="s">
+        <v>228</v>
+      </c>
+      <c r="D131" s="237"/>
+      <c r="E131" s="237"/>
+      <c r="F131" s="237"/>
+      <c r="G131" s="237"/>
+      <c r="H131" s="237"/>
+      <c r="I131" s="237"/>
+      <c r="J131" s="237"/>
+      <c r="K131" s="237"/>
+      <c r="L131" s="237"/>
+      <c r="M131" s="237"/>
     </row>
     <row r="132" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C132" s="230"/>
-      <c r="D132" s="230"/>
-      <c r="E132" s="230"/>
-      <c r="F132" s="230"/>
-      <c r="G132" s="230"/>
-      <c r="H132" s="230"/>
-      <c r="I132" s="230"/>
-      <c r="J132" s="230"/>
-      <c r="K132" s="230"/>
-      <c r="L132" s="230"/>
-      <c r="M132" s="230"/>
+      <c r="C132" s="237"/>
+      <c r="D132" s="237"/>
+      <c r="E132" s="237"/>
+      <c r="F132" s="237"/>
+      <c r="G132" s="237"/>
+      <c r="H132" s="237"/>
+      <c r="I132" s="237"/>
+      <c r="J132" s="237"/>
+      <c r="K132" s="237"/>
+      <c r="L132" s="237"/>
+      <c r="M132" s="237"/>
     </row>
     <row r="133" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C133" s="230"/>
-      <c r="D133" s="230"/>
-      <c r="E133" s="230"/>
-      <c r="F133" s="230"/>
-      <c r="G133" s="230"/>
-      <c r="H133" s="230"/>
-      <c r="I133" s="230"/>
-      <c r="J133" s="230"/>
-      <c r="K133" s="230"/>
-      <c r="L133" s="230"/>
-      <c r="M133" s="230"/>
+      <c r="C133" s="237"/>
+      <c r="D133" s="237"/>
+      <c r="E133" s="237"/>
+      <c r="F133" s="237"/>
+      <c r="G133" s="237"/>
+      <c r="H133" s="237"/>
+      <c r="I133" s="237"/>
+      <c r="J133" s="237"/>
+      <c r="K133" s="237"/>
+      <c r="L133" s="237"/>
+      <c r="M133" s="237"/>
     </row>
     <row r="134" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C134" s="230"/>
-      <c r="D134" s="230"/>
-      <c r="E134" s="230"/>
-      <c r="F134" s="230"/>
-      <c r="G134" s="230"/>
-      <c r="H134" s="230"/>
-      <c r="I134" s="230"/>
-      <c r="J134" s="230"/>
-      <c r="K134" s="230"/>
-      <c r="L134" s="230"/>
-      <c r="M134" s="230"/>
+      <c r="C134" s="237"/>
+      <c r="D134" s="237"/>
+      <c r="E134" s="237"/>
+      <c r="F134" s="237"/>
+      <c r="G134" s="237"/>
+      <c r="H134" s="237"/>
+      <c r="I134" s="237"/>
+      <c r="J134" s="237"/>
+      <c r="K134" s="237"/>
+      <c r="L134" s="237"/>
+      <c r="M134" s="237"/>
     </row>
     <row r="135" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C135" s="230"/>
-      <c r="D135" s="230"/>
-      <c r="E135" s="230"/>
-      <c r="F135" s="230"/>
-      <c r="G135" s="230"/>
-      <c r="H135" s="230"/>
-      <c r="I135" s="230"/>
-      <c r="J135" s="230"/>
-      <c r="K135" s="230"/>
-      <c r="L135" s="230"/>
-      <c r="M135" s="230"/>
+      <c r="C135" s="237"/>
+      <c r="D135" s="237"/>
+      <c r="E135" s="237"/>
+      <c r="F135" s="237"/>
+      <c r="G135" s="237"/>
+      <c r="H135" s="237"/>
+      <c r="I135" s="237"/>
+      <c r="J135" s="237"/>
+      <c r="K135" s="237"/>
+      <c r="L135" s="237"/>
+      <c r="M135" s="237"/>
     </row>
     <row r="136" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C136" s="230"/>
-      <c r="D136" s="230"/>
-      <c r="E136" s="230"/>
-      <c r="F136" s="230"/>
-      <c r="G136" s="230"/>
-      <c r="H136" s="230"/>
-      <c r="I136" s="230"/>
-      <c r="J136" s="230"/>
-      <c r="K136" s="230"/>
-      <c r="L136" s="230"/>
-      <c r="M136" s="230"/>
+      <c r="C136" s="237"/>
+      <c r="D136" s="237"/>
+      <c r="E136" s="237"/>
+      <c r="F136" s="237"/>
+      <c r="G136" s="237"/>
+      <c r="H136" s="237"/>
+      <c r="I136" s="237"/>
+      <c r="J136" s="237"/>
+      <c r="K136" s="237"/>
+      <c r="L136" s="237"/>
+      <c r="M136" s="237"/>
     </row>
     <row r="137" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C137" s="230"/>
-      <c r="D137" s="230"/>
-      <c r="E137" s="230"/>
-      <c r="F137" s="230"/>
-      <c r="G137" s="230"/>
-      <c r="H137" s="230"/>
-      <c r="I137" s="230"/>
-      <c r="J137" s="230"/>
-      <c r="K137" s="230"/>
-      <c r="L137" s="230"/>
-      <c r="M137" s="230"/>
+      <c r="C137" s="237"/>
+      <c r="D137" s="237"/>
+      <c r="E137" s="237"/>
+      <c r="F137" s="237"/>
+      <c r="G137" s="237"/>
+      <c r="H137" s="237"/>
+      <c r="I137" s="237"/>
+      <c r="J137" s="237"/>
+      <c r="K137" s="237"/>
+      <c r="L137" s="237"/>
+      <c r="M137" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C131:M137"/>
     <mergeCell ref="C128:M129"/>
@@ -9840,6 +9789,11 @@
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9864,7 +9818,7 @@
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
       <c r="D1" s="48" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1" s="48"/>
       <c r="F1" s="47"/>
@@ -9874,7 +9828,7 @@
       <c r="J1" s="47"/>
       <c r="K1" s="47"/>
       <c r="L1" s="48" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M1" s="47"/>
       <c r="N1" s="50" t="str">
@@ -9888,7 +9842,7 @@
       <c r="B2" s="49"/>
       <c r="C2" s="49"/>
       <c r="D2" s="48" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E2" s="47"/>
       <c r="F2" s="47"/>
@@ -9913,7 +9867,7 @@
       <c r="H3" s="47"/>
       <c r="I3" s="47"/>
       <c r="J3" s="48" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K3" s="48"/>
       <c r="L3" s="51">
@@ -9936,7 +9890,7 @@
       <c r="H4" s="47"/>
       <c r="I4" s="47"/>
       <c r="J4" s="48" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K4" s="48"/>
       <c r="L4" s="51">
@@ -9947,91 +9901,91 @@
       <c r="O4" s="47"/>
     </row>
     <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="244" t="s">
+      <c r="A5" s="247" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="247" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="247" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="53" t="s">
+      <c r="H5" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="244" t="s">
+      <c r="J5" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="39"/>
+      <c r="N5" s="247" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="O5" s="247" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="36" t="s">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="248"/>
+      <c r="B6" s="248"/>
+      <c r="C6" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5" s="37" t="s">
+      <c r="E6" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="39"/>
-      <c r="N5" s="244" t="s">
+      <c r="F6" s="248"/>
+      <c r="G6" s="42" t="s">
         <v>56</v>
-      </c>
-      <c r="O5" s="244" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="245"/>
-      <c r="B6" s="245"/>
-      <c r="C6" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="245"/>
-      <c r="G6" s="42" t="s">
-        <v>59</v>
       </c>
       <c r="H6" s="43">
         <v>0.06</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K6" s="45" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L6" s="42" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M6" s="45"/>
-      <c r="N6" s="245"/>
-      <c r="O6" s="245"/>
+      <c r="N6" s="248"/>
+      <c r="O6" s="248"/>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>1</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C7" s="85">
         <v>5.4</v>
@@ -10077,7 +10031,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" s="85">
         <v>5.5</v>
@@ -10123,7 +10077,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C9" s="85">
         <v>4.5</v>
@@ -10169,7 +10123,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C10" s="85">
         <v>6.1</v>
@@ -10215,7 +10169,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="82" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" s="85">
         <v>5.4</v>
@@ -10261,7 +10215,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="83" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" s="85">
         <v>5</v>
@@ -10307,7 +10261,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="82" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C13" s="85">
         <v>5</v>
@@ -10353,7 +10307,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C14" s="85">
         <v>4.9000000000000004</v>
@@ -10399,7 +10353,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="82" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" s="85">
         <v>4.9000000000000004</v>
@@ -10445,7 +10399,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="82" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C16" s="85">
         <v>5.9</v>
@@ -10491,7 +10445,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="82" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C17" s="85">
         <v>5.7</v>
@@ -10537,7 +10491,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="82" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C18" s="85">
         <v>5.4</v>
@@ -10583,7 +10537,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="82" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C19" s="85">
         <v>5.5</v>
@@ -10629,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="82" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="85">
         <v>4.5</v>
@@ -10675,7 +10629,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="82" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21" s="85">
         <v>6.1</v>
@@ -10721,7 +10675,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="82" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C22" s="85">
         <v>5.4</v>
@@ -10767,7 +10721,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="82" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C23" s="85">
         <v>5</v>
@@ -10813,7 +10767,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="82" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C24" s="85">
         <v>5</v>
@@ -10859,7 +10813,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="82" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C25" s="85">
         <v>4.9000000000000004</v>
@@ -10905,7 +10859,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="82" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C26" s="85">
         <v>4.9000000000000004</v>
@@ -10951,7 +10905,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="82" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C27" s="85">
         <v>5.9</v>
@@ -10997,7 +10951,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="84" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C28" s="85">
         <v>5.7</v>
